--- a/naver-place-crawler/results_health/전주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/전주_헬스장.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4691</v>
+        <v>4715</v>
       </c>
       <c r="Q2" t="n">
         <v>231</v>
       </c>
       <c r="R2" t="n">
-        <v>4922</v>
+        <v>4946</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="Q3" t="n">
         <v>464</v>
       </c>
       <c r="R3" t="n">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마이짐&amp;GDR아카데미</t>
+          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mygym0203@naver.com</t>
+          <t>onewayeco@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1361-0338</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산북로 11-3 301호,303호</t>
+          <t>전북 전주시 덕진구 화암4길 60 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mygym0203/224148941542</t>
+          <t>https://www.instagram.com/onewayfitness3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w3hkyj4</t>
+          <t>https://talk.naver.com/ct/wwzxui7</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>173</v>
+        <v>1305</v>
       </c>
       <c r="Q4" t="n">
-        <v>237</v>
+        <v>331</v>
       </c>
       <c r="R4" t="n">
-        <v>410</v>
+        <v>1636</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1842506959</t>
+          <t>1857733969</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1842506959</t>
+          <t>https://m.place.naver.com/place/1857733969</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -858,25 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>24시 헬스 PT 제로백피트니스 효자점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1399-8873</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>https://blog.naver.com/zeroback2022/223179008503</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
+          <t>https://talk.naver.com/ct/w5ycz5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>253</v>
+        <v>1253</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>421</v>
       </c>
       <c r="R5" t="n">
-        <v>280</v>
+        <v>1674</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>1709963411</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/1709963411</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -952,29 +952,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>하이짐 헬스&amp;PT 평화점</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>higym_official@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1375-7398</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym_official</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,15 +985,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="Q6" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2060819661</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060819661</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1132,46 +1132,46 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>사람휘트니스 서신16호점</t>
+          <t>짐플릭스 송천점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hoy04245@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1412-6116</t>
+          <t>0507-1382-8094</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 서신로 62 지리산빌딩 5층</t>
+          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/saramfitness_seosin</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5z5kr</t>
+          <t>https://talk.naver.com/ct/w23okib</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>96</v>
+        <v>627</v>
       </c>
       <c r="Q8" t="n">
-        <v>123</v>
+        <v>860</v>
       </c>
       <c r="R8" t="n">
-        <v>219</v>
+        <v>1487</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1974601302</t>
+          <t>1027880481</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1974601302</t>
+          <t>https://m.place.naver.com/place/1027880481</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐플릭스 송천점</t>
+          <t>짐플릭스 평화점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1253,18 +1253,18 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1382-8094</t>
+          <t>0507-1408-8909</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w23okib</t>
+          <t>https://talk.naver.com/ct/wwx54rl</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>625</v>
+        <v>479</v>
       </c>
       <c r="Q9" t="n">
-        <v>860</v>
+        <v>882</v>
       </c>
       <c r="R9" t="n">
-        <v>1485</v>
+        <v>1361</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1027880481</t>
+          <t>1336256244</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027880481</t>
+          <t>https://m.place.naver.com/place/1336256244</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐플릭스 평화점</t>
+          <t>짐플릭스 송천2호점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1351,18 +1351,18 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1408-8909</t>
+          <t>0507-1484-8094</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 모악로 4678 7층</t>
+          <t>전북 전주시 덕진구 시천로 35 용진빌딩 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr/</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwx54rl</t>
+          <t>https://talk.naver.com/ct/wws0fj1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>479</v>
+        <v>144</v>
       </c>
       <c r="Q10" t="n">
-        <v>882</v>
+        <v>574</v>
       </c>
       <c r="R10" t="n">
-        <v>1361</v>
+        <v>718</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1336256244</t>
+          <t>2051918606</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336256244</t>
+          <t>https://m.place.naver.com/place/2051918606</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>카이로짐 체형관리 PT샵 효천점</t>
+          <t>카이로짐 체형관�� PT샵 효천점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hyesungda@naver.com</t>
+          <t>jinho3014@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/전주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/전주_헬스장.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4720</v>
+        <v>4728</v>
       </c>
       <c r="Q2" t="n">
         <v>231</v>
       </c>
       <c r="R2" t="n">
-        <v>4951</v>
+        <v>4959</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -858,25 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
+          <t>24시 헬스 PT 제로백피트니스 효자점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>onewayeco@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1399-8873</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 화암4길 60 4층</t>
+          <t>전북 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onewayfitness3</t>
+          <t>https://blog.naver.com/zeroback2022/223179008503</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwzxui7</t>
+          <t>https://talk.naver.com/ct/w5ycz5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1305</v>
+        <v>1253</v>
       </c>
       <c r="Q5" t="n">
-        <v>331</v>
+        <v>421</v>
       </c>
       <c r="R5" t="n">
-        <v>1636</v>
+        <v>1674</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1857733969</t>
+          <t>1709963411</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857733969</t>
+          <t>https://m.place.naver.com/place/1709963411</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,29 +956,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 효자점</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1399-8873</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223179008503</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ycz5</t>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1253</v>
+        <v>261</v>
       </c>
       <c r="Q6" t="n">
-        <v>421</v>
+        <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>1674</v>
+        <v>288</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1709963411</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709963411</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,25 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>온탑피트니스 만성점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>ontopfit@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1355-5810</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>https://blog.naver.com/ontopfit</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
+          <t>https://talk.naver.com/ct/w4egfn</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>260</v>
+        <v>175</v>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>280</v>
       </c>
       <c r="R7" t="n">
-        <v>287</v>
+        <v>455</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>1089561368</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/1089561368</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1144,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>온탑피트니스 만성점</t>
+          <t>하이짐 헬스&amp;PT 평화점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ontopfit@naver.com</t>
+          <t>higym_official@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1355-5810</t>
+          <t>0507-1375-7398</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ontopfit</t>
+          <t>https://blog.naver.com/higym_official</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1186,17 +1190,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4egfn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="Q8" t="n">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="R8" t="n">
-        <v>455</v>
+        <v>301</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1089561368</t>
+          <t>2060819661</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089561368</t>
+          <t>https://m.place.naver.com/place/2060819661</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐플릭스 평화점</t>
+          <t>프리덤휘트니스 효자점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymflix063@naver.com</t>
+          <t>dks8980@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1408-8909</t>
+          <t>063-226-8980</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 모악로 4678 7층</t>
+          <t>전북 전주시 완산구 홍산1길 12 3층 프리덤휘트니스 전주효자점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr/</t>
+          <t>https://blog.naver.com/dks8980</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwx54rl</t>
+          <t>https://talk.naver.com/ct/wg8k7fd</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>479</v>
+        <v>176</v>
       </c>
       <c r="Q9" t="n">
-        <v>882</v>
+        <v>183</v>
       </c>
       <c r="R9" t="n">
-        <v>1361</v>
+        <v>359</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1336256244</t>
+          <t>384238641</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336256244</t>
+          <t>https://m.place.naver.com/place/384238641</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐플릭스 송천점</t>
+          <t>짐플릭스 평화점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1351,18 +1351,18 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1382-8094</t>
+          <t>0507-1408-8909</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w23okib</t>
+          <t>https://talk.naver.com/ct/wwx54rl</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>627</v>
+        <v>479</v>
       </c>
       <c r="Q10" t="n">
-        <v>860</v>
+        <v>882</v>
       </c>
       <c r="R10" t="n">
-        <v>1487</v>
+        <v>1361</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1027880481</t>
+          <t>1336256244</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027880481</t>
+          <t>https://m.place.naver.com/place/1336256244</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,39 +1438,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>카이로짐 체형관리 PT샵 효천점</t>
+          <t>짐플릭스 송천점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hyesungda@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1415-5022</t>
+          <t>0507-1382-8094</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
+          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ftdy</t>
+          <t>https://talk.naver.com/ct/w23okib</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,17 +1495,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>68</v>
+        <v>626</v>
       </c>
       <c r="Q11" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="R11" t="n">
-        <v>144</v>
+        <v>1486</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1693804133</t>
+          <t>1027880481</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693804133</t>
+          <t>https://m.place.naver.com/place/1027880481</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/전주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/전주_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 효자점</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1399-8873</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223179008503</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ycz5</t>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1253</v>
+        <v>261</v>
       </c>
       <c r="Q5" t="n">
-        <v>421</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
-        <v>1674</v>
+        <v>288</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1709963411</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709963411</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -956,25 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>하이짐 헬스&amp;PT 평화점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>higym_official@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1375-7398</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>https://blog.naver.com/higym_official</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,22 +989,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="R6" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>2060819661</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/2060819661</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1132,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>하이짐 헬스&amp;PT 평화점</t>
+          <t>사람휘트니스 서신16호점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>higym_official@naver.com</t>
+          <t>hoy04245@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1375-7398</t>
+          <t>0507-1412-6116</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북 전주시 완산구 서신로 62 지리산빌딩 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym_official</t>
+          <t>https://www.instagram.com/saramfitness_seosin</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,18 +1181,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5z5kr</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="Q8" t="n">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="R8" t="n">
-        <v>301</v>
+        <v>219</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2060819661</t>
+          <t>1974601302</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060819661</t>
+          <t>https://m.place.naver.com/place/1974601302</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1404,10 +1404,10 @@
         <v>479</v>
       </c>
       <c r="Q10" t="n">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="R10" t="n">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,105 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>카이로짐 체형관리 PT샵 효천점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hyesungda@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1415-5022</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ftdy</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>76</v>
+      </c>
+      <c r="R12" t="n">
+        <v>144</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1693804133</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1693804133</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/전주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/전주_헬스장.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -726,10 +726,10 @@
         <v>1101</v>
       </c>
       <c r="Q3" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="R3" t="n">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -858,12 +858,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>onewayeco@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -871,12 +871,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 덕진구 화암4길 60 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>https://www.instagram.com/onewayfitness3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
+          <t>https://talk.naver.com/ct/wwzxui7</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>261</v>
+        <v>1305</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>331</v>
       </c>
       <c r="R5" t="n">
-        <v>288</v>
+        <v>1636</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>1857733969</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/1857733969</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,29 +952,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>하이짐 헬스&amp;PT 평화점</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>higym_official@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1375-7398</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym_official</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,18 +985,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>222</v>
+        <v>261</v>
       </c>
       <c r="Q6" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2060819661</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060819661</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1046,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>온탑피트니스 만성점</t>
+          <t>하이짐 헬스&amp;PT 평화점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ontopfit@naver.com</t>
+          <t>higym_official@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1355-5810</t>
+          <t>0507-1375-7398</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ontopfit</t>
+          <t>https://blog.naver.com/higym_official</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1088,17 +1088,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4egfn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="Q7" t="n">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="R7" t="n">
-        <v>455</v>
+        <v>301</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1118,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1089561368</t>
+          <t>2060819661</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089561368</t>
+          <t>https://m.place.naver.com/place/2060819661</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1144,29 +1140,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>사람휘트니스 서신16호점</t>
+          <t>온탑피트니스 만성점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hoy04245@naver.com</t>
+          <t>ontopfit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1412-6116</t>
+          <t>0507-1355-5810</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 서신로 62 지리산빌딩 5층</t>
+          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/saramfitness_seosin</t>
+          <t>https://blog.naver.com/ontopfit</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,7 +1177,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1191,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5z5kr</t>
+          <t>https://talk.naver.com/ct/w4egfn</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="Q8" t="n">
-        <v>123</v>
+        <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>219</v>
+        <v>455</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1216,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1974601302</t>
+          <t>1089561368</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1974601302</t>
+          <t>https://m.place.naver.com/place/1089561368</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">

--- a/naver-place-crawler/results_health/전주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/전주_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4728</v>
+        <v>4729</v>
       </c>
       <c r="Q2" t="n">
         <v>231</v>
       </c>
       <c r="R2" t="n">
-        <v>4959</v>
+        <v>4960</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="Q3" t="n">
         <v>464</v>
       </c>
       <c r="R3" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="Q5" t="n">
         <v>331</v>
       </c>
       <c r="R5" t="n">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -952,25 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>24시 헬스 PT 제로백피트니스 효자점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1399-8873</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>https://blog.naver.com/zeroback2022/223179008503</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -995,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
+          <t>https://talk.naver.com/ct/w5ycz5</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1009,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>261</v>
+        <v>1254</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>423</v>
       </c>
       <c r="R6" t="n">
-        <v>288</v>
+        <v>1677</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>1709963411</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/1709963411</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1046,29 +1050,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>하이짐 헬스&amp;PT 평화점</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>higym_official@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1375-7398</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym_official</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,18 +1083,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1103,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="Q7" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="R7" t="n">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2060819661</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060819661</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1135,34 +1139,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>온탑피트니스 만성점</t>
+          <t>프리덤휘트니스 효자점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ontopfit@naver.com</t>
+          <t>dks8980@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1355-5810</t>
+          <t>063-226-8980</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+          <t>전북 전주시 완산구 홍산1길 12 3층 프리덤휘트니스 전주효자점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ontopfit</t>
+          <t>https://blog.naver.com/dks8980</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1187,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4egfn</t>
+          <t>https://talk.naver.com/ct/wg8k7fd</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="n">
-        <v>280</v>
+        <v>183</v>
       </c>
       <c r="R8" t="n">
-        <v>455</v>
+        <v>359</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1089561368</t>
+          <t>384238641</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089561368</t>
+          <t>https://m.place.naver.com/place/384238641</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,34 +1242,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>프리덤휘트니스 효자점</t>
+          <t>짐플릭스 평화점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dks8980@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>063-226-8980</t>
+          <t>0507-1408-8909</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산1길 12 3층 프리덤휘트니스 전주효자점</t>
+          <t>전북 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dks8980</t>
+          <t>https://gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1275,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wg8k7fd</t>
+          <t>https://talk.naver.com/ct/wwx54rl</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>176</v>
+        <v>479</v>
       </c>
       <c r="Q9" t="n">
-        <v>183</v>
+        <v>884</v>
       </c>
       <c r="R9" t="n">
-        <v>359</v>
+        <v>1363</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>384238641</t>
+          <t>1336256244</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/384238641</t>
+          <t>https://m.place.naver.com/place/1336256244</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,7 +1340,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐플릭스 평화점</t>
+          <t>짐플릭스 송천점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1347,18 +1351,18 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1408-8909</t>
+          <t>0507-1382-8094</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 모악로 4678 7층</t>
+          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr/</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwx54rl</t>
+          <t>https://talk.naver.com/ct/w23okib</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>479</v>
+        <v>633</v>
       </c>
       <c r="Q10" t="n">
-        <v>883</v>
+        <v>861</v>
       </c>
       <c r="R10" t="n">
-        <v>1362</v>
+        <v>1494</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1336256244</t>
+          <t>1027880481</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336256244</t>
+          <t>https://m.place.naver.com/place/1027880481</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,39 +1438,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐플릭스 송천점</t>
+          <t>카이로짐 체형관리 PT샵 효천점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gymflix063@naver.com</t>
+          <t>hyesungda@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1382-8094</t>
+          <t>0507-1415-5022</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1481,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w23okib</t>
+          <t>https://talk.naver.com/ct/w4ftdy</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1491,17 +1495,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>626</v>
+        <v>68</v>
       </c>
       <c r="Q11" t="n">
-        <v>860</v>
+        <v>76</v>
       </c>
       <c r="R11" t="n">
-        <v>1486</v>
+        <v>144</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,113 +1514,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1027880481</t>
+          <t>1693804133</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027880481</t>
+          <t>https://m.place.naver.com/place/1693804133</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>카이로짐 체형관리 PT샵 효천점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>hyesungda@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1415-5022</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ftdy</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>76</v>
-      </c>
-      <c r="R12" t="n">
-        <v>144</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1693804133</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1693804133</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/전주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/전주_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4729</v>
+        <v>4730</v>
       </c>
       <c r="Q2" t="n">
         <v>231</v>
       </c>
       <c r="R2" t="n">
-        <v>4960</v>
+        <v>4961</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>onewayeco@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -871,12 +871,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 화암4길 60 4층</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onewayfitness3</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwzxui7</t>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1306</v>
+        <v>264</v>
       </c>
       <c r="Q5" t="n">
-        <v>331</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
-        <v>1637</v>
+        <v>291</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1857733969</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857733969</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 효자점</t>
+          <t>온탑피트니스 만성점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>ontopfit@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1399-8873</t>
+          <t>0507-1355-5810</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
+          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223179008503</t>
+          <t>https://blog.naver.com/ontopfit</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ycz5</t>
+          <t>https://talk.naver.com/ct/w4egfn</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1254</v>
+        <v>176</v>
       </c>
       <c r="Q6" t="n">
-        <v>423</v>
+        <v>280</v>
       </c>
       <c r="R6" t="n">
-        <v>1677</v>
+        <v>456</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1709963411</t>
+          <t>1089561368</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709963411</t>
+          <t>https://m.place.naver.com/place/1089561368</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1050,25 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>하이짐 헬스&amp;PT 평화점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>higym_official@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1375-7398</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>https://blog.naver.com/higym_official</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,22 +1087,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="R7" t="n">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,51 +1122,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>2060819661</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/2060819661</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>프리덤휘트니스 효자점</t>
+          <t>사람휘트니스 서신16호점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dks8980@naver.com</t>
+          <t>hoy04245@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>063-226-8980</t>
+          <t>0507-1412-6116</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산1길 12 3층 프리덤휘트니스 전주효자점</t>
+          <t>전북 전주시 완산구 서신로 62 지리산빌딩 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dks8980</t>
+          <t>https://www.instagram.com/saramfitness_seosin</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wg8k7fd</t>
+          <t>https://talk.naver.com/ct/w5z5kr</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>176</v>
+        <v>96</v>
       </c>
       <c r="Q8" t="n">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="R8" t="n">
-        <v>359</v>
+        <v>219</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>384238641</t>
+          <t>1974601302</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/384238641</t>
+          <t>https://m.place.naver.com/place/1974601302</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1242,34 +1242,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐플릭스 평화점</t>
+          <t>프리덤휘트니스 효자점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymflix063@naver.com</t>
+          <t>dks8980@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1408-8909</t>
+          <t>063-226-8980</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 모악로 4678 7층</t>
+          <t>전북 전주시 완산구 홍산1길 12 3층 프리덤휘트니스 전주효자점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr/</t>
+          <t>https://blog.naver.com/dks8980</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwx54rl</t>
+          <t>https://talk.naver.com/ct/wg8k7fd</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>479</v>
+        <v>176</v>
       </c>
       <c r="Q9" t="n">
-        <v>884</v>
+        <v>184</v>
       </c>
       <c r="R9" t="n">
-        <v>1363</v>
+        <v>360</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1336256244</t>
+          <t>384238641</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336256244</t>
+          <t>https://m.place.naver.com/place/384238641</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐플릭스 송천점</t>
+          <t>짐플릭스 평화점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1351,18 +1351,18 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1382-8094</t>
+          <t>0507-1408-8909</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w23okib</t>
+          <t>https://talk.naver.com/ct/wwx54rl</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>633</v>
+        <v>479</v>
       </c>
       <c r="Q10" t="n">
-        <v>861</v>
+        <v>884</v>
       </c>
       <c r="R10" t="n">
-        <v>1494</v>
+        <v>1363</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1027880481</t>
+          <t>1336256244</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027880481</t>
+          <t>https://m.place.naver.com/place/1336256244</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1438,93 +1438,191 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>카이로짐 체형관리 PT샵 효천점</t>
+          <t>짐플릭스 송천점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hyesungda@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1415-5022</t>
+          <t>0507-1382-8094</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.gymflix.co.kr/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w23okib</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>639</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>862</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1501</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1027880481</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1027880481</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>카이로짐 체형관리 PT샵 효천점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hyesungda@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1415-5022</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w4ftdy</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>68</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>76</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>144</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1693804133</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1693804133</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/전주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/전주_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4730</v>
+        <v>4737</v>
       </c>
       <c r="Q2" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="R2" t="n">
-        <v>4961</v>
+        <v>4970</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="Q3" t="n">
         <v>464</v>
       </c>
       <c r="R3" t="n">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         <v>177</v>
       </c>
       <c r="Q4" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="R4" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -858,12 +858,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>원웨이피트니스 송천에코점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>onewayeco@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -871,12 +871,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 덕진구 화암4길 60 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>https://www.instagram.com/onewayfitness3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
+          <t>https://talk.naver.com/ct/wwzxui7</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>264</v>
+        <v>1307</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>331</v>
       </c>
       <c r="R5" t="n">
-        <v>291</v>
+        <v>1638</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>1857733969</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/1857733969</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>온탑피트니스 만성점</t>
+          <t>24시 헬스 PT 제로백피트니스 효자점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ontopfit@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1355-5810</t>
+          <t>0507-1399-8873</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+          <t>전북 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ontopfit</t>
+          <t>https://blog.naver.com/zeroback2022/223179008503</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4egfn</t>
+          <t>https://talk.naver.com/ct/w5ycz5</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>176</v>
+        <v>1255</v>
       </c>
       <c r="Q6" t="n">
-        <v>280</v>
+        <v>425</v>
       </c>
       <c r="R6" t="n">
-        <v>456</v>
+        <v>1680</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1089561368</t>
+          <t>1709963411</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089561368</t>
+          <t>https://m.place.naver.com/place/1709963411</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,29 +1050,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>하이짐 헬스&amp;PT 평화점</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>higym_official@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1375-7398</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym_official</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,18 +1083,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="Q7" t="n">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="R7" t="n">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2060819661</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060819661</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1144,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>사람휘트니스 서신16호점</t>
+          <t>온탑피트니스 만성점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hoy04245@naver.com</t>
+          <t>ontopfit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1412-6116</t>
+          <t>0507-1355-5810</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 서신로 62 지리산빌딩 5층</t>
+          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/saramfitness_seosin</t>
+          <t>https://blog.naver.com/ontopfit</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5z5kr</t>
+          <t>https://talk.naver.com/ct/w4egfn</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="n">
-        <v>123</v>
+        <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>219</v>
+        <v>456</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1974601302</t>
+          <t>1089561368</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1974601302</t>
+          <t>https://m.place.naver.com/place/1089561368</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>프리덤휘트니스 효자점</t>
+          <t>짐플릭스 평화점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dks8980@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>063-226-8980</t>
+          <t>0507-1408-8909</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산1길 12 3층 프리덤휘트니스 전주효자점</t>
+          <t>전북 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dks8980</t>
+          <t>https://gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wg8k7fd</t>
+          <t>https://talk.naver.com/ct/wwx54rl</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>176</v>
+        <v>480</v>
       </c>
       <c r="Q9" t="n">
-        <v>184</v>
+        <v>884</v>
       </c>
       <c r="R9" t="n">
-        <v>360</v>
+        <v>1364</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>384238641</t>
+          <t>1336256244</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/384238641</t>
+          <t>https://m.place.naver.com/place/1336256244</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐플릭스 평화점</t>
+          <t>짐플릭스 송천점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1351,18 +1351,18 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1408-8909</t>
+          <t>0507-1382-8094</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 모악로 4678 7층</t>
+          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr/</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwx54rl</t>
+          <t>https://talk.naver.com/ct/w23okib</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>479</v>
+        <v>641</v>
       </c>
       <c r="Q10" t="n">
-        <v>884</v>
+        <v>862</v>
       </c>
       <c r="R10" t="n">
-        <v>1363</v>
+        <v>1503</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1336256244</t>
+          <t>1027880481</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336256244</t>
+          <t>https://m.place.naver.com/place/1027880481</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,39 +1438,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐플릭스 송천점</t>
+          <t>카이로짐 체형관리 PT샵 효천점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gymflix063@naver.com</t>
+          <t>hyesungda@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1382-8094</t>
+          <t>0507-1415-5022</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w23okib</t>
+          <t>https://talk.naver.com/ct/w4ftdy</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,17 +1495,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>639</v>
+        <v>68</v>
       </c>
       <c r="Q11" t="n">
-        <v>862</v>
+        <v>76</v>
       </c>
       <c r="R11" t="n">
-        <v>1501</v>
+        <v>144</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,113 +1514,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1027880481</t>
+          <t>1693804133</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027880481</t>
+          <t>https://m.place.naver.com/place/1693804133</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>카이로짐 체형관리 PT샵 효천점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>hyesungda@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1415-5022</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ftdy</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>76</v>
-      </c>
-      <c r="R12" t="n">
-        <v>144</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1693804133</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1693804133</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/전주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/전주_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4737</v>
+        <v>4738</v>
       </c>
       <c r="Q2" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R2" t="n">
-        <v>4970</v>
+        <v>4972</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="Q3" t="n">
         <v>464</v>
       </c>
       <c r="R3" t="n">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -952,29 +952,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 효자점</t>
+          <t>브루짐 헬스&amp;PT 효자점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>brewgym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1399-8873</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 용머리로 11 2층 제로백피트니스</t>
+          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223179008503</t>
+          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,7 +985,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +995,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ycz5</t>
+          <t>https://talk.naver.com/ct/wr0wz2v</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1255</v>
+        <v>268</v>
       </c>
       <c r="Q6" t="n">
-        <v>425</v>
+        <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>1680</v>
+        <v>295</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1709963411</t>
+          <t>2009027135</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709963411</t>
+          <t>https://m.place.naver.com/place/2009027135</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1050,25 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브루짐 헬스&amp;PT 효자점</t>
+          <t>온탑피트니스 만성점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>brewgym@naver.com</t>
+          <t>ontopfit@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1355-5810</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 호암로 67 큰사랑빌딩 2층</t>
+          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brewgym_official?igsh=cXlzZ3VrYzduZXAy</t>
+          <t>https://blog.naver.com/ontopfit</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wr0wz2v</t>
+          <t>https://talk.naver.com/ct/w4egfn</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>266</v>
+        <v>176</v>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>280</v>
       </c>
       <c r="R7" t="n">
-        <v>293</v>
+        <v>456</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2009027135</t>
+          <t>1089561368</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009027135</t>
+          <t>https://m.place.naver.com/place/1089561368</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>온탑피트니스 만성점</t>
+          <t>하이짐 헬스&amp;PT 평화점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ontopfit@naver.com</t>
+          <t>higym_official@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1355-5810</t>
+          <t>0507-1375-7398</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성중앙로 76 4층 온탑피트니스</t>
+          <t>전북 전주시 완산구 평화18길 29 4층 하이짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ontopfit</t>
+          <t>https://blog.naver.com/higym_official</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1186,14 +1186,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4egfn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="Q8" t="n">
-        <v>280</v>
+        <v>81</v>
       </c>
       <c r="R8" t="n">
-        <v>456</v>
+        <v>307</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1089561368</t>
+          <t>2060819661</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089561368</t>
+          <t>https://m.place.naver.com/place/2060819661</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1242,34 +1238,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐플릭스 평화점</t>
+          <t>프리덤휘트니스 효자점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymflix063@naver.com</t>
+          <t>dks8980@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1408-8909</t>
+          <t>063-226-8980</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 모악로 4678 7층</t>
+          <t>전북 전주시 완산구 홍산1길 12 3층 프리덤휘트니스 전주효자점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr/</t>
+          <t>https://blog.naver.com/dks8980</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,7 +1275,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwx54rl</t>
+          <t>https://talk.naver.com/ct/wg8k7fd</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>480</v>
+        <v>176</v>
       </c>
       <c r="Q9" t="n">
-        <v>884</v>
+        <v>185</v>
       </c>
       <c r="R9" t="n">
-        <v>1364</v>
+        <v>361</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1314,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1336256244</t>
+          <t>384238641</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336256244</t>
+          <t>https://m.place.naver.com/place/384238641</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1336,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐플릭스 송천점</t>
+          <t>짐플릭스 평화점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1351,18 +1347,18 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1382-8094</t>
+          <t>0507-1408-8909</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+          <t>전북 전주시 완산구 모악로 4678 7층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w23okib</t>
+          <t>https://talk.naver.com/ct/wwx54rl</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>641</v>
+        <v>480</v>
       </c>
       <c r="Q10" t="n">
-        <v>862</v>
+        <v>884</v>
       </c>
       <c r="R10" t="n">
-        <v>1503</v>
+        <v>1364</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1412,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1027880481</t>
+          <t>1336256244</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027880481</t>
+          <t>https://m.place.naver.com/place/1336256244</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1438,93 +1434,191 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>카이로짐 체형관리 PT샵 효천점</t>
+          <t>짐플릭스 송천점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hyesungda@naver.com</t>
+          <t>gymflix063@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1415-5022</t>
+          <t>0507-1382-8094</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>전북 전주시 덕진구 솔내로 131 4층 401,402호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.gymflix.co.kr/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w23okib</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>641</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>862</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1027880481</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1027880481</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>카이로짐 체형관리 PT샵 효천점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hyesungda@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1415-5022</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>전북 전주시 완산구 홍산로 14 트윈빌딩B 401호</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w4ftdy</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>68</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>76</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>144</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1693804133</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1693804133</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
